--- a/Data/Processed Data/anonymized_google_play_reviews.xlsx
+++ b/Data/Processed Data/anonymized_google_play_reviews.xlsx
@@ -41843,7 +41843,7 @@
       </c>
       <c r="E1657" t="inlineStr">
         <is>
-          <t>I would like to speak with the manager about the money I lost on &lt;DATE&gt;</t>
+          <t>I would like to speak with the manager about the money I lost on 16/10/2025</t>
         </is>
       </c>
     </row>
